--- a/Team-Data/2013-14/3-10-2013-14.xlsx
+++ b/Team-Data/2013-14/3-10-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
         <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>0.435</v>
+        <v>0.426</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
@@ -679,7 +746,7 @@
         <v>37.7</v>
       </c>
       <c r="J2" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0.459</v>
@@ -691,64 +758,64 @@
         <v>25.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O2" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P2" t="n">
         <v>21.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.78</v>
+        <v>0.778</v>
       </c>
       <c r="R2" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S2" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T2" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U2" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="V2" t="n">
         <v>15.3</v>
       </c>
       <c r="W2" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z2" t="n">
         <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.7</v>
+        <v>101.5</v>
       </c>
       <c r="AC2" t="n">
         <v>-1</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AE2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF2" t="n">
         <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH2" t="n">
         <v>10</v>
@@ -769,7 +836,7 @@
         <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
         <v>21</v>
@@ -793,10 +860,10 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
         <v>25</v>
@@ -808,7 +875,7 @@
         <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE3" t="n">
         <v>24</v>
@@ -954,10 +1021,10 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
         <v>11</v>
@@ -969,7 +1036,7 @@
         <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU3" t="n">
         <v>24</v>
@@ -981,7 +1048,7 @@
         <v>22</v>
       </c>
       <c r="AX3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
         <v>15</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4" t="n">
         <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>0.516</v>
+        <v>0.508</v>
       </c>
       <c r="H4" t="n">
         <v>48.4</v>
@@ -1043,10 +1110,10 @@
         <v>35.3</v>
       </c>
       <c r="J4" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L4" t="n">
         <v>8.1</v>
@@ -1055,28 +1122,28 @@
         <v>22.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.364</v>
+        <v>0.361</v>
       </c>
       <c r="O4" t="n">
         <v>18.7</v>
       </c>
       <c r="P4" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="R4" t="n">
         <v>8.9</v>
       </c>
       <c r="S4" t="n">
-        <v>29.3</v>
+        <v>29.5</v>
       </c>
       <c r="T4" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="U4" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V4" t="n">
         <v>14.5</v>
@@ -1091,25 +1158,25 @@
         <v>4.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA4" t="n">
         <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
         <v>15</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
         <v>15</v>
@@ -1127,22 +1194,22 @@
         <v>14</v>
       </c>
       <c r="AL4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM4" t="n">
         <v>11</v>
       </c>
       <c r="AN4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO4" t="n">
         <v>10</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
         <v>29</v>
@@ -1160,16 +1227,16 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY4" t="n">
         <v>8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA4" t="n">
         <v>11</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5" t="n">
         <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>0.469</v>
+        <v>0.46</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
@@ -1231,25 +1298,25 @@
         <v>0.438</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M5" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O5" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.732</v>
+        <v>0.73</v>
       </c>
       <c r="R5" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S5" t="n">
         <v>32.7</v>
@@ -1264,7 +1331,7 @@
         <v>12.5</v>
       </c>
       <c r="W5" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X5" t="n">
         <v>5.1</v>
@@ -1279,13 +1346,13 @@
         <v>21.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.59999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1309,13 +1376,13 @@
         <v>25</v>
       </c>
       <c r="AL5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM5" t="n">
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO5" t="n">
         <v>12</v>
@@ -1327,10 +1394,10 @@
         <v>24</v>
       </c>
       <c r="AR5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
         <v>22</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1491,7 +1558,7 @@
         <v>28</v>
       </c>
       <c r="AL6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM6" t="n">
         <v>27</v>
@@ -1500,7 +1567,7 @@
         <v>25</v>
       </c>
       <c r="AO6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP6" t="n">
         <v>16</v>
@@ -1524,7 +1591,7 @@
         <v>26</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX6" t="n">
         <v>9</v>
@@ -1542,7 +1609,7 @@
         <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -1649,16 +1716,16 @@
         <v>-4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF7" t="n">
         <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH7" t="n">
         <v>3</v>
@@ -1694,7 +1761,7 @@
         <v>4</v>
       </c>
       <c r="AS7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1855,7 +1922,7 @@
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM8" t="n">
         <v>12</v>
@@ -1867,7 +1934,7 @@
         <v>18</v>
       </c>
       <c r="AP8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1891,7 +1958,7 @@
         <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E9" t="n">
         <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>0.429</v>
+        <v>0.435</v>
       </c>
       <c r="H9" t="n">
         <v>48.2</v>
@@ -1959,25 +2026,25 @@
         <v>0.446</v>
       </c>
       <c r="L9" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M9" t="n">
         <v>23.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="O9" t="n">
         <v>18.8</v>
       </c>
       <c r="P9" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.717</v>
+        <v>0.718</v>
       </c>
       <c r="R9" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S9" t="n">
         <v>32.9</v>
@@ -1986,13 +2053,13 @@
         <v>45.3</v>
       </c>
       <c r="U9" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V9" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W9" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X9" t="n">
         <v>5.7</v>
@@ -2007,28 +2074,28 @@
         <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.3</v>
+        <v>103.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
         <v>5</v>
@@ -2043,7 +2110,7 @@
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2064,13 +2131,13 @@
         <v>4</v>
       </c>
       <c r="AU9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
         <v>27</v>
       </c>
       <c r="AW9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -2195,19 +2262,19 @@
         <v>-2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
         <v>8</v>
@@ -2249,7 +2316,7 @@
         <v>21</v>
       </c>
       <c r="AV10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
         <v>4</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,7 +2456,7 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>6</v>
@@ -2407,10 +2474,10 @@
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2443,7 +2510,7 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA11" t="n">
         <v>19</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>5</v>
       </c>
       <c r="AD12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>5</v>
@@ -2580,16 +2647,16 @@
         <v>28</v>
       </c>
       <c r="AK12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM12" t="n">
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2625,7 +2692,7 @@
         <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>6.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2753,7 +2820,7 @@
         <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
         <v>22</v>
@@ -2765,19 +2832,19 @@
         <v>13</v>
       </c>
       <c r="AL13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="n">
         <v>24</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
         <v>5</v>
@@ -2795,13 +2862,13 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
       </c>
       <c r="AX13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY13" t="n">
         <v>14</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14" t="n">
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
@@ -2863,16 +2930,16 @@
         <v>39</v>
       </c>
       <c r="J14" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="L14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="N14" t="n">
         <v>0.351</v>
@@ -2899,19 +2966,19 @@
         <v>24.4</v>
       </c>
       <c r="V14" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W14" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X14" t="n">
         <v>4.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA14" t="n">
         <v>23.9</v>
@@ -2941,10 +3008,10 @@
         <v>7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2977,10 +3044,10 @@
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX14" t="n">
         <v>18</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -3105,16 +3172,16 @@
         <v>-5.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>24</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH15" t="n">
         <v>29</v>
@@ -3147,7 +3214,7 @@
         <v>18</v>
       </c>
       <c r="AR15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS15" t="n">
         <v>13</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>10</v>
@@ -3305,7 +3372,7 @@
         <v>17</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
         <v>8</v>
@@ -3326,7 +3393,7 @@
         <v>29</v>
       </c>
       <c r="AQ16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
@@ -3335,7 +3402,7 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F17" t="n">
         <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>0.721</v>
+        <v>0.717</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
@@ -3418,37 +3485,37 @@
         <v>8.1</v>
       </c>
       <c r="M17" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.372</v>
+        <v>0.37</v>
       </c>
       <c r="O17" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P17" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R17" t="n">
         <v>7.5</v>
       </c>
       <c r="S17" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T17" t="n">
         <v>36.8</v>
       </c>
       <c r="U17" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V17" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W17" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X17" t="n">
         <v>4.5</v>
@@ -3457,22 +3524,22 @@
         <v>3</v>
       </c>
       <c r="Z17" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>104</v>
+        <v>104.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD17" t="n">
         <v>30</v>
       </c>
       <c r="AE17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF17" t="n">
         <v>2</v>
@@ -3502,13 +3569,13 @@
         <v>10</v>
       </c>
       <c r="AO17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3523,19 +3590,19 @@
         <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
         <v>2</v>
       </c>
       <c r="AX17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>15</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F18" t="n">
         <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>0.206</v>
+        <v>0.194</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
@@ -3594,40 +3661,40 @@
         <v>82.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.43</v>
+        <v>0.429</v>
       </c>
       <c r="L18" t="n">
         <v>7.3</v>
       </c>
       <c r="M18" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O18" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P18" t="n">
         <v>21.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R18" t="n">
         <v>11.8</v>
       </c>
       <c r="S18" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T18" t="n">
         <v>41.4</v>
       </c>
       <c r="U18" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V18" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W18" t="n">
         <v>6.7</v>
@@ -3636,22 +3703,22 @@
         <v>5.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="n">
         <v>20.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3687,13 +3754,13 @@
         <v>27</v>
       </c>
       <c r="AP18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
         <v>28</v>
@@ -3717,7 +3784,7 @@
         <v>19</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -3833,10 +3900,10 @@
         <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF19" t="n">
         <v>16</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -4015,10 +4082,10 @@
         <v>-2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF20" t="n">
         <v>20</v>
@@ -4054,7 +4121,7 @@
         <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
         <v>7</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -4119,55 +4186,55 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F21" t="n">
         <v>40</v>
       </c>
       <c r="G21" t="n">
-        <v>0.385</v>
+        <v>0.375</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J21" t="n">
-        <v>83.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0.446</v>
+        <v>0.444</v>
       </c>
       <c r="L21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M21" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O21" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="P21" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.747</v>
+        <v>0.75</v>
       </c>
       <c r="R21" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S21" t="n">
         <v>29.9</v>
       </c>
       <c r="T21" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U21" t="n">
         <v>20.4</v>
@@ -4176,7 +4243,7 @@
         <v>13.1</v>
       </c>
       <c r="W21" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X21" t="n">
         <v>4.6</v>
@@ -4188,13 +4255,13 @@
         <v>22.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>98.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
       <c r="AD21" t="n">
         <v>1</v>
@@ -4206,13 +4273,13 @@
         <v>22</v>
       </c>
       <c r="AG21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH21" t="n">
         <v>8</v>
       </c>
       <c r="AI21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ21" t="n">
         <v>13</v>
@@ -4221,13 +4288,13 @@
         <v>20</v>
       </c>
       <c r="AL21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM21" t="n">
         <v>5</v>
       </c>
-      <c r="AM21" t="n">
-        <v>4</v>
-      </c>
       <c r="AN21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
         <v>27</v>
@@ -4257,16 +4324,16 @@
         <v>16</v>
       </c>
       <c r="AX21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ21" t="n">
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4391,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI22" t="n">
         <v>4</v>
@@ -4400,7 +4467,7 @@
         <v>18</v>
       </c>
       <c r="AK22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL22" t="n">
         <v>16</v>
@@ -4415,7 +4482,7 @@
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -4483,22 +4550,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23" t="n">
         <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G23" t="n">
-        <v>0.292</v>
+        <v>0.297</v>
       </c>
       <c r="H23" t="n">
         <v>48.7</v>
       </c>
       <c r="I23" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J23" t="n">
         <v>83.2</v>
@@ -4507,25 +4574,25 @@
         <v>0.443</v>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M23" t="n">
         <v>19.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O23" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="P23" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.764</v>
+        <v>0.765</v>
       </c>
       <c r="R23" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S23" t="n">
         <v>32.7</v>
@@ -4534,7 +4601,7 @@
         <v>42.3</v>
       </c>
       <c r="U23" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V23" t="n">
         <v>14.5</v>
@@ -4546,13 +4613,13 @@
         <v>4.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z23" t="n">
         <v>20.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="AB23" t="n">
         <v>96.8</v>
@@ -4573,7 +4640,7 @@
         <v>28</v>
       </c>
       <c r="AH23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI23" t="n">
         <v>21</v>
@@ -4597,16 +4664,16 @@
         <v>25</v>
       </c>
       <c r="AP23" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
         <v>20</v>
@@ -4621,13 +4688,13 @@
         <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY23" t="n">
         <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G24" t="n">
-        <v>0.238</v>
+        <v>0.242</v>
       </c>
       <c r="H24" t="n">
         <v>48.6</v>
@@ -4686,22 +4753,22 @@
         <v>88.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.433</v>
+        <v>0.432</v>
       </c>
       <c r="L24" t="n">
         <v>6.7</v>
       </c>
       <c r="M24" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.305</v>
+        <v>0.306</v>
       </c>
       <c r="O24" t="n">
         <v>16.8</v>
       </c>
       <c r="P24" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q24" t="n">
         <v>0.714</v>
@@ -4710,13 +4777,13 @@
         <v>11.8</v>
       </c>
       <c r="S24" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T24" t="n">
         <v>43.7</v>
       </c>
       <c r="U24" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V24" t="n">
         <v>17.4</v>
@@ -4737,13 +4804,13 @@
         <v>20.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="AC24" t="n">
         <v>-11.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4758,7 +4825,7 @@
         <v>7</v>
       </c>
       <c r="AI24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ24" t="n">
         <v>1</v>
@@ -4779,13 +4846,13 @@
         <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
         <v>14</v>
@@ -4794,7 +4861,7 @@
         <v>12</v>
       </c>
       <c r="AU24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E25" t="n">
         <v>36</v>
       </c>
       <c r="F25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25" t="n">
-        <v>0.571</v>
+        <v>0.581</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4874,7 +4941,7 @@
         <v>9.4</v>
       </c>
       <c r="M25" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="N25" t="n">
         <v>0.376</v>
@@ -4886,25 +4953,25 @@
         <v>24.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.759</v>
+        <v>0.761</v>
       </c>
       <c r="R25" t="n">
         <v>11.6</v>
       </c>
       <c r="S25" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T25" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U25" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="V25" t="n">
         <v>15.3</v>
       </c>
       <c r="W25" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X25" t="n">
         <v>4.7</v>
@@ -4916,31 +4983,31 @@
         <v>22.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB25" t="n">
         <v>105.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ25" t="n">
         <v>10</v>
@@ -4952,10 +5019,10 @@
         <v>4</v>
       </c>
       <c r="AM25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
         <v>9</v>
@@ -4964,13 +5031,13 @@
         <v>9</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
         <v>13</v>
       </c>
       <c r="AS25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT25" t="n">
         <v>13</v>
@@ -4979,10 +5046,10 @@
         <v>29</v>
       </c>
       <c r="AV25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX25" t="n">
         <v>14</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>4.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5161,7 +5228,7 @@
         <v>6</v>
       </c>
       <c r="AV26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
@@ -5170,7 +5237,7 @@
         <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ26" t="n">
         <v>7</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5304,7 +5371,7 @@
         <v>12</v>
       </c>
       <c r="AI27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ27" t="n">
         <v>17</v>
@@ -5349,7 +5416,7 @@
         <v>19</v>
       </c>
       <c r="AX27" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AY27" t="n">
         <v>22</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>6.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5525,7 +5592,7 @@
         <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
         <v>18</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -5575,61 +5642,61 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29" t="n">
         <v>35</v>
       </c>
       <c r="F29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.574</v>
       </c>
       <c r="H29" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I29" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J29" t="n">
-        <v>82.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L29" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M29" t="n">
         <v>22.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.367</v>
+        <v>0.369</v>
       </c>
       <c r="O29" t="n">
         <v>19.2</v>
       </c>
       <c r="P29" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R29" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S29" t="n">
         <v>31.3</v>
       </c>
       <c r="T29" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U29" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V29" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W29" t="n">
         <v>6.9</v>
@@ -5638,28 +5705,28 @@
         <v>4.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z29" t="n">
         <v>23</v>
       </c>
       <c r="AA29" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.3</v>
+        <v>100.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
       </c>
       <c r="AF29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG29" t="n">
         <v>12</v>
@@ -5671,19 +5738,19 @@
         <v>25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK29" t="n">
         <v>22</v>
       </c>
       <c r="AL29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO29" t="n">
         <v>6</v>
@@ -5701,7 +5768,7 @@
         <v>19</v>
       </c>
       <c r="AT29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU29" t="n">
         <v>16</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -5757,46 +5824,46 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E30" t="n">
         <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G30" t="n">
-        <v>0.344</v>
+        <v>0.349</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
       </c>
       <c r="I30" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J30" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K30" t="n">
         <v>0.442</v>
       </c>
       <c r="L30" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M30" t="n">
         <v>19.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
       <c r="O30" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P30" t="n">
         <v>21.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.748</v>
+        <v>0.747</v>
       </c>
       <c r="R30" t="n">
         <v>11</v>
@@ -5805,7 +5872,7 @@
         <v>30.6</v>
       </c>
       <c r="T30" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U30" t="n">
         <v>20</v>
@@ -5814,7 +5881,7 @@
         <v>14.7</v>
       </c>
       <c r="W30" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="X30" t="n">
         <v>4.7</v>
@@ -5823,31 +5890,31 @@
         <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA30" t="n">
         <v>20.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.8</v>
+        <v>94.5</v>
       </c>
       <c r="AC30" t="n">
         <v>-6</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE30" t="n">
         <v>24</v>
       </c>
       <c r="AF30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH30" t="n">
         <v>26</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>27</v>
       </c>
       <c r="AI30" t="n">
         <v>26</v>
@@ -5865,16 +5932,16 @@
         <v>23</v>
       </c>
       <c r="AN30" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP30" t="n">
         <v>21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR30" t="n">
         <v>19</v>
@@ -5901,7 +5968,7 @@
         <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA30" t="n">
         <v>16</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E31" t="n">
         <v>33</v>
       </c>
       <c r="F31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G31" t="n">
-        <v>0.524</v>
+        <v>0.532</v>
       </c>
       <c r="H31" t="n">
         <v>49</v>
@@ -5957,46 +6024,46 @@
         <v>38.7</v>
       </c>
       <c r="J31" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L31" t="n">
         <v>8</v>
       </c>
       <c r="M31" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="N31" t="n">
         <v>0.387</v>
       </c>
       <c r="O31" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P31" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="Q31" t="n">
         <v>0.728</v>
       </c>
       <c r="R31" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S31" t="n">
         <v>31.4</v>
       </c>
       <c r="T31" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U31" t="n">
         <v>23.4</v>
       </c>
       <c r="V31" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W31" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X31" t="n">
         <v>4.7</v>
@@ -6005,19 +6072,19 @@
         <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.7</v>
+        <v>100.9</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6032,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ31" t="n">
         <v>8</v>
@@ -6053,19 +6120,19 @@
         <v>28</v>
       </c>
       <c r="AP31" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AQ31" t="n">
         <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS31" t="n">
         <v>18</v>
       </c>
       <c r="AT31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU31" t="n">
         <v>7</v>
@@ -6074,10 +6141,10 @@
         <v>13</v>
       </c>
       <c r="AW31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6086,13 +6153,13 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>16</v>
       </c>
       <c r="BC31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-10-2013-14</t>
+          <t>2014-03-10</t>
         </is>
       </c>
     </row>
